--- a/TrackGestora_v2.xlsx
+++ b/TrackGestora_v2.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x15 xr xr6 xr10">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
@@ -8,23 +8,22 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Carlo Taranto\Progetti_Tech\Personali\Gestora\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C8C16CE0-3C13-4976-BEF7-A110F5E3D01B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{981BE711-BB5C-498D-A384-164F474C3ABA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1920" yWindow="1920" windowWidth="30960" windowHeight="12120"/>
+    <workbookView xWindow="18984" yWindow="0" windowWidth="22296" windowHeight="16560" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Oggi" sheetId="1" r:id="rId1"/>
+    <sheet name="Oggi" sheetId="6" r:id="rId1"/>
     <sheet name="Referto" sheetId="2" r:id="rId2"/>
     <sheet name="Fatte" sheetId="3" r:id="rId3"/>
     <sheet name="Decisioni" sheetId="4" r:id="rId4"/>
     <sheet name="Diario" sheetId="5" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">Decisioni!$A$4:$E$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Diario!$A$4:$C$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Fatte!$A$4:$E$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Oggi!$A$4:$H$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Referto!$A$4:$H$4</definedName>
+    <definedName name="_FilterDatabase" localSheetId="3" hidden="1">Decisioni!$A$4:$E$4</definedName>
+    <definedName name="_FilterDatabase" localSheetId="4" hidden="1">Diario!$A$4:$C$4</definedName>
+    <definedName name="_FilterDatabase" localSheetId="2" hidden="1">Fatte!$A$4:$E$4</definedName>
+    <definedName name="_FilterDatabase" localSheetId="1" hidden="1">Referto!$A$4:$H$4</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -47,14 +46,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="173">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="182">
   <si>
     <t>Oggi — cosa manca</t>
   </si>
   <si>
-    <t>Il foglio che apri ogni mattina. Contiene SOLO le righe aperte, in ordine di priorita'. Quando una e' finita si mette Fatto, e a fine sessione si sposta in Fatte: cosi' questo foglio resta corto per costruzione. Se non sai scrivere la colonna "Perche' conta", la riga non serve.</t>
-  </si>
-  <si>
     <t>ID</t>
   </si>
   <si>
@@ -67,27 +63,12 @@
     <t>Area</t>
   </si>
   <si>
-    <t>Priorita'</t>
-  </si>
-  <si>
     <t>Stato</t>
   </si>
   <si>
-    <t>Chi</t>
-  </si>
-  <si>
-    <t>Aggiornato</t>
-  </si>
-  <si>
     <t>OP-01</t>
   </si>
   <si>
-    <t>Pushare il branch dev su origin</t>
-  </si>
-  <si>
-    <t>I 3 commit del redesign «Turno» esistono solo su questo PC: oggi non c'e' nessuna copia altrove</t>
-  </si>
-  <si>
     <t>Operazioni</t>
   </si>
   <si>
@@ -103,12 +84,6 @@
     <t>BE-01</t>
   </si>
   <si>
-    <t>Chiudere CAP-001: il tetto dei coperti non e' garantito dal database</t>
-  </si>
-  <si>
-    <t>Due prenotazioni simultanee sulla stessa fascia possono sforare il tetto (56 coperti su 52) e nessuno se ne accorge</t>
-  </si>
-  <si>
     <t>Backend</t>
   </si>
   <si>
@@ -118,36 +93,15 @@
     <t>BE-02</t>
   </si>
   <si>
-    <t>Audit del backend: concorrenza, autorizzazioni, validazione, errori, job, cache, schema</t>
-  </si>
-  <si>
-    <t>Serve sapere cosa c'e' prima di decidere cosa sistemare. Produce le righe del foglio Referto</t>
-  </si>
-  <si>
-    <t>Claude</t>
-  </si>
-  <si>
     <t>FE-01</t>
   </si>
   <si>
-    <t>Prova a schermo del redesign con GestoraDocs/verifica-redesign.md</t>
-  </si>
-  <si>
-    <t>Il redesign e' stato scritto e misurato, mai guardato: e' l'unico punto cieco rimasto</t>
-  </si>
-  <si>
     <t>Frontend</t>
   </si>
   <si>
     <t>FE-02</t>
   </si>
   <si>
-    <t>Audit del frontend: i 3 cambi di comportamento dopo 059c0d5, sicurezza, test, form</t>
-  </si>
-  <si>
-    <t>Il redesign ha toccato 72 file. Tre di quei cambi non sono aspetto ma comportamento</t>
-  </si>
-  <si>
     <t>FE-03</t>
   </si>
   <si>
@@ -163,42 +117,15 @@
     <t>DOC-01</t>
   </si>
   <si>
-    <t>Aprire AppuntiFix.txt e trasformarlo in righe di questo tracker</t>
-  </si>
-  <si>
-    <t>Sono i miglioramenti notati usando l'app davvero: probabilmente i piu' utili di tutti</t>
-  </si>
-  <si>
     <t>Documenti</t>
   </si>
   <si>
     <t>DOC-02</t>
   </si>
   <si>
-    <t>Aggiornare CLAUDE.md paragrafo 8 perche' punti a questo tracker</t>
-  </si>
-  <si>
-    <t>Finche' punta al vecchio, ogni sessione riparte aggiornando il file sbagliato</t>
-  </si>
-  <si>
     <t>DB-01</t>
   </si>
   <si>
-    <t>Reset completo dei due database (procedura nel RUNBOOK)</t>
-  </si>
-  <si>
-    <t>Toglie i dati di prova accumulati. Va fatto per ultimo, altrimenti si rifa' daccapo</t>
-  </si>
-  <si>
-    <t>Database</t>
-  </si>
-  <si>
-    <t>Quando capita</t>
-  </si>
-  <si>
-    <t>Pianificato</t>
-  </si>
-  <si>
     <t>OP-02</t>
   </si>
   <si>
@@ -566,13 +493,112 @@
   </si>
   <si>
     <t>F</t>
+  </si>
+  <si>
+    <t>L'audit si legge per aree, e ogni area sblocca subito i propri fix. Non e' un blocco unico da aspettare tutto</t>
+  </si>
+  <si>
+    <t>Aspettare la fine di tutto l'audit prima di correggere / correggere BE-01 subito, prima dell'audit</t>
+  </si>
+  <si>
+    <t>Correggere BE-01 prima di A1 significa scegliere una strategia guardando una sola corsa: se A1 ne trova altre tre nello stesso servizio (unione tavoli, cambio fascia, cancellazione zona) il primo fix va rifatto. Aspettare tutto l'audit invece tiene fermo per giorni un difetto gia' diagnosticato. L'ordine vero e' A1 -&gt; fix BE-01 -&gt; resto dell'audit -&gt; resto dei fix</t>
+  </si>
+  <si>
+    <t>Valutato e scartato il reset a 059c0d5 dopo aver misurato cosa era stato toccato (backend: 2 soli file, zero righe nei Services). Definito il programma per la v1.1: audit, triage, correzioni in ordine di rischio. Creato questo tracker, congelato il vecchio, aggiornato CLAUDE.md. Misurata la baseline.</t>
+  </si>
+  <si>
+    <t>Ognuno fa la propria lista dall'alto in basso. Il numero 1 e' la prossima cosa da fare: non c'e' altro da decidere. Quando una riga e' finita si mette Fatto, e a fine sessione si sposta nel foglio Fatte; le altre risalgono di un numero.</t>
+  </si>
+  <si>
+    <t>TOCCA A TE</t>
+  </si>
+  <si>
+    <t>N.</t>
+  </si>
+  <si>
+    <t>Prova a schermo del redesign: lancia il seed, poi le prime dieci voci di GestoraDocs/verifica-redesign.md</t>
+  </si>
+  <si>
+    <t>Il redesign e' stato scritto e misurato, mai guardato. E' l'unico punto cieco rimasto, e nessuno puo' farlo al posto tuo</t>
+  </si>
+  <si>
+    <t>Passarmi AppuntiFix.txt: lo leggiamo insieme e ogni punto diventa una riga qui</t>
+  </si>
+  <si>
+    <t>Sono i miglioramenti che hai notato usando l'app davvero: probabilmente i piu' utili di tutti</t>
+  </si>
+  <si>
+    <t>Reset completo dei due database, seguendo il RUNBOOK</t>
+  </si>
+  <si>
+    <t>Toglie i dati di prova accumulati. Va fatto quando non c'e' piu' niente da implementare, altrimenti si rifa' daccapo</t>
+  </si>
+  <si>
+    <t>Per ultimo</t>
+  </si>
+  <si>
+    <t>TOCCA A CLAUDE</t>
+  </si>
+  <si>
+    <t>Audit del backend, area A1: concorrenza e integrita' dei dati</t>
+  </si>
+  <si>
+    <t>Dice se le corse come quella dei coperti sono una sola o quattro, e quindi quale strategia usare per chiuderle. Sblocca la riga 2</t>
+  </si>
+  <si>
+    <t>Chiudere il buco sul tetto dei coperti (CAP-001)</t>
+  </si>
+  <si>
+    <t>Due prenotazioni simultanee sulla stessa fascia possono sforare il tetto: 56 coperti su 52, e la Dashboard non lo mostra</t>
+  </si>
+  <si>
+    <t>BE-03</t>
+  </si>
+  <si>
+    <t>Audit del backend, aree A2-A8: autorizzazioni, validazione, errori, algoritmo tavoli, job, cache, schema</t>
+  </si>
+  <si>
+    <t>A2 e' la piu' pesante: 9 controller, 3 ruoli, e nessun test copre il caso di un Cliente che chiede i dati di un altro</t>
+  </si>
+  <si>
+    <t>Audit del frontend: i 3 cambi di comportamento dopo 059c0d5, sicurezza, copertura dei test, form</t>
+  </si>
+  <si>
+    <t>Il redesign ha toccato 72 file. Tre di quei cambi non sono aspetto ma comportamento, e vanno guardati uno per uno</t>
+  </si>
+  <si>
+    <t>INSIEME, quando l'audit e' finito: si legge il foglio Referto riga per riga e per ognuna si decide "si sistema" / "dopo" / "non si fa". Poi si correggono i difetti in ordine di gravita'.</t>
+  </si>
+  <si>
+    <t>Pushare il branch dev su origin: i 3 commit del redesign non erano piu' solo su questo PC</t>
+  </si>
+  <si>
+    <t>git status -sb dice "## dev...origin/dev" senza ahead; su GitHub il commit 804f7c5 c'e'</t>
+  </si>
+  <si>
+    <t>CLAUDE.md aggiornato al nuovo tracker: sezioni 3, 8 e 9</t>
+  </si>
+  <si>
+    <t>Riletto il file: nessun riferimento residuo al vecchio tracker come attivo</t>
+  </si>
+  <si>
+    <t>Il foglio Oggi e' due liste numerate, una per persona, da fare dall'alto in basso</t>
+  </si>
+  <si>
+    <t>Lista unica ordinata per priorita', con colonne Chi / Priorita' / Dipende da</t>
+  </si>
+  <si>
+    <t>La prima versione chiedeva di tenere in testa tre cose insieme - priorita', proprietario e dipendenze - per rispondere a una domanda sola: cosa faccio adesso. Con due liste numerate la domanda ha una risposta sola e visibile, e le dipendenze spariscono perche' sono gia' dentro l'ordine</t>
+  </si>
+  <si>
+    <t>Fase 0 chiusa e pushata. Il foglio Oggi e' stato rifatto: due liste numerate invece di una lista con priorita' e dipendenze, perche' la prima versione non diceva da dove riprendere. Domani: Fabio dalla riga 1 della sua lista, Claude dalla riga 1 della sua.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="5" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -612,8 +638,24 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -641,6 +683,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFDDE9F7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC55A11"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4472C4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -672,10 +726,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -692,6 +745,13 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -1025,412 +1085,309 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H17"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5444F316-A297-40ED-AE53-3C364C398DCE}">
+  <dimension ref="A1:E22"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.77734375" customWidth="1"/>
-    <col min="2" max="2" width="52.77734375" customWidth="1"/>
-    <col min="3" max="3" width="62.77734375" customWidth="1"/>
-    <col min="4" max="4" width="13.77734375" customWidth="1"/>
-    <col min="5" max="5" width="15.77734375" customWidth="1"/>
-    <col min="6" max="6" width="11.77734375" customWidth="1"/>
-    <col min="7" max="7" width="10.77734375" customWidth="1"/>
-    <col min="8" max="8" width="13.77734375" customWidth="1"/>
+    <col min="1" max="1" width="5.77734375" customWidth="1"/>
+    <col min="2" max="2" width="10.77734375" customWidth="1"/>
+    <col min="3" max="3" width="66.77734375" customWidth="1"/>
+    <col min="4" max="4" width="72.77734375" customWidth="1"/>
+    <col min="5" max="5" width="12.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="21" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:5" ht="21" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" s="8" t="s">
+        <v>153</v>
+      </c>
+      <c r="B2" s="8"/>
+      <c r="C2" s="8"/>
+      <c r="D2" s="8"/>
+      <c r="E2" s="8"/>
+    </row>
+    <row r="4" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A4" s="9" t="s">
+        <v>154</v>
+      </c>
+      <c r="B4" s="9"/>
+      <c r="C4" s="9"/>
+      <c r="D4" s="9"/>
+      <c r="E4" s="9"/>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A4" s="4" t="s">
+      <c r="C5" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="D5" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="E5" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A6" s="10">
+        <v>1</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="10">
+        <v>2</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8" s="10">
+        <v>3</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" s="10">
         <v>4</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="B9" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A10" s="10">
         <v>5</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="B10" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A11" s="10">
         <v>6</v>
       </c>
-      <c r="F4" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="H4" s="4" t="s">
+      <c r="B11" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A13" s="11" t="s">
+        <v>163</v>
+      </c>
+      <c r="B13" s="11"/>
+      <c r="C13" s="11"/>
+      <c r="D13" s="11"/>
+      <c r="E13" s="11"/>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A14" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A15" s="10">
+        <v>1</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="E15" s="6" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A5" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="B5" s="5" t="s">
+    <row r="16" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A16" s="10">
+        <v>2</v>
+      </c>
+      <c r="B16" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="F5" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="G5" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="H5" s="6">
-        <v>46274</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A6" s="5" t="s">
+      <c r="C16" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="E16" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A17" s="10">
+        <v>3</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A18" s="10">
+        <v>4</v>
+      </c>
+      <c r="B18" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="C18" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A19" s="10">
+        <v>5</v>
+      </c>
+      <c r="B19" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C19" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="D19" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="E6" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="F6" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="G6" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="H6" s="6">
-        <v>46274</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A7" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="F7" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="G7" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="H7" s="6">
-        <v>46274</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A8" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="F8" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="G8" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="H8" s="6">
-        <v>46274</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A9" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="F9" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="G9" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="H9" s="6">
-        <v>46274</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A10" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="C10" s="5" t="s">
+      <c r="E19" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A20" s="10">
+        <v>6</v>
+      </c>
+      <c r="B20" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="D10" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="E10" s="5" t="s">
+      <c r="C20" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F10" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="G10" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="H10" s="6">
-        <v>46274</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A11" s="5" t="s">
+      <c r="D20" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="B11" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="D11" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="E11" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="F11" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="G11" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="H11" s="6">
-        <v>46274</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A12" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="D12" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="E12" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="F12" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="G12" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="H12" s="6">
-        <v>46274</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A13" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="D13" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="E13" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="F13" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="G13" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="H13" s="6">
-        <v>46274</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A14" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="D14" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="E14" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="F14" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="G14" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="H14" s="6">
-        <v>46274</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A15" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="D15" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="E15" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="F15" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="G15" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="H15" s="6">
-        <v>46274</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A16" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="B16" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="C16" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="D16" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="E16" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="F16" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="G16" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="H16" s="6">
-        <v>46274</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A17" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="B17" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="D17" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="E17" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="F17" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="G17" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="H17" s="6">
-        <v>46274</v>
-      </c>
+      <c r="E20" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A22" s="12" t="s">
+        <v>173</v>
+      </c>
+      <c r="B22" s="12"/>
+      <c r="C22" s="12"/>
+      <c r="D22" s="12"/>
+      <c r="E22" s="12"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:H4"/>
-  <mergeCells count="1">
-    <mergeCell ref="A2:H2"/>
+  <mergeCells count="4">
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="A13:E13"/>
+    <mergeCell ref="A22:E22"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:H14"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -1445,229 +1402,229 @@
   <sheetData>
     <row r="1" spans="1:8" ht="21" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="B2" s="8"/>
+      <c r="C2" s="8"/>
+      <c r="D2" s="8"/>
+      <c r="E2" s="8"/>
+      <c r="F2" s="8"/>
+      <c r="G2" s="8"/>
+      <c r="H2" s="8"/>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A4" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A5" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="H5" s="5">
+        <v>46274</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A6" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="H6" s="5">
+        <v>46274</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A7" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="H7" s="5">
+        <v>46274</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A8" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="E8" s="4" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
+      <c r="F8" s="4"/>
+      <c r="G8" s="4"/>
+      <c r="H8" s="5">
+        <v>46274</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A9" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A4" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4" s="4" t="s">
+      <c r="B9" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D9" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="E9" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="F9" s="4"/>
+      <c r="G9" s="4"/>
+      <c r="H9" s="5">
+        <v>46274</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A10" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="B10" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="G4" s="4" t="s">
+      <c r="D10" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="H4" s="4" t="s">
+      <c r="E10" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="G10" s="4" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="5" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A5" s="5" t="s">
+      <c r="H10" s="5">
+        <v>46274</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A11" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="B5" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C5" s="5" t="s">
+      <c r="B11" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C11" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="D11" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="E5" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="F5" s="5" t="s">
+      <c r="E11" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="F11" s="4"/>
+      <c r="G11" s="4"/>
+      <c r="H11" s="5">
+        <v>46274</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A13" s="2" t="s">
         <v>73</v>
-      </c>
-      <c r="G5" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="H5" s="6">
-        <v>46274</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A6" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="G6" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="H6" s="6">
-        <v>46274</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A7" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="G7" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="H7" s="6">
-        <v>46274</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A8" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="F8" s="5"/>
-      <c r="G8" s="5"/>
-      <c r="H8" s="6">
-        <v>46274</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A9" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="F9" s="5"/>
-      <c r="G9" s="5"/>
-      <c r="H9" s="6">
-        <v>46274</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A10" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>91</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="E10" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="F10" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="G10" s="5" t="s">
-        <v>93</v>
-      </c>
-      <c r="H10" s="6">
-        <v>46274</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A11" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>95</v>
-      </c>
-      <c r="D11" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="E11" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="F11" s="5"/>
-      <c r="G11" s="5"/>
-      <c r="H11" s="6">
-        <v>46274</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A13" s="3" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>98</v>
+        <v>74</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:H4"/>
+  <autoFilter ref="A4:H4" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
   <mergeCells count="1">
     <mergeCell ref="A2:H2"/>
   </mergeCells>
@@ -1676,8 +1633,8 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E6"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:E8"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.77734375" customWidth="1"/>
@@ -1689,71 +1646,105 @@
   <sheetData>
     <row r="1" spans="1:5" ht="21" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
-        <v>99</v>
+        <v>75</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
+      <c r="A2" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="B2" s="8"/>
+      <c r="C2" s="8"/>
+      <c r="D2" s="8"/>
+      <c r="E2" s="8"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>102</v>
+      <c r="C4" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A5" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="D5" s="6">
+      <c r="A5" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D5" s="5">
         <v>46274</v>
       </c>
-      <c r="E5" s="5" t="s">
-        <v>105</v>
+      <c r="E5" s="4" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A6" s="5" t="s">
-        <v>106</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>107</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="D6" s="6">
+      <c r="A6" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D6" s="5">
         <v>46274</v>
       </c>
-      <c r="E6" s="5" t="s">
-        <v>108</v>
+      <c r="E6" s="4" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A7" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D7" s="5">
+        <v>46274</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D8" s="5">
+        <v>46274</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>177</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:E4"/>
+  <autoFilter ref="A4:E4" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
   <mergeCells count="1">
     <mergeCell ref="A2:E2"/>
   </mergeCells>
@@ -1762,8 +1753,8 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E21"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <dimension ref="A1:E23"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.77734375" customWidth="1"/>
@@ -1775,326 +1766,360 @@
   <sheetData>
     <row r="1" spans="1:5" ht="21" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="B2" s="8"/>
+      <c r="C2" s="8"/>
+      <c r="D2" s="8"/>
+      <c r="E2" s="8"/>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A5" s="5">
+        <v>46274</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A6" s="5">
+        <v>46274</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A7" s="5">
+        <v>46274</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A8" s="5">
+        <v>46274</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A9" s="5">
+        <v>46274</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A10" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="D10" s="4" t="s">
         <v>109</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
+      <c r="E10" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A11" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="B11" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="B4" s="4" t="s">
+      <c r="C11" s="4" t="s">
         <v>111</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="D11" s="4" t="s">
         <v>112</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="E11" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A12" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="B12" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="C12" s="4" t="s">
         <v>114</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A5" s="6">
+      <c r="D12" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A13" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A14" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A17" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A18" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A19" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="E19" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A20" s="5">
+        <v>46243</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="E20" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A21" s="5">
+        <v>46243</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="E21" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A22" s="5">
         <v>46274</v>
       </c>
-      <c r="B5" s="5" t="s">
-        <v>115</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>116</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>117</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A6" s="6">
+      <c r="B22" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="E22" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A23" s="5">
         <v>46274</v>
       </c>
-      <c r="B6" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>119</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>120</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A7" s="6">
-        <v>46274</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>121</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>123</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A8" s="6">
-        <v>46274</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>126</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A9" s="6">
-        <v>46274</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>127</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>128</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A10" s="5" t="s">
-        <v>130</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>131</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>132</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="E10" s="5" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A11" s="5" t="s">
-        <v>130</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>134</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="D11" s="5" t="s">
-        <v>136</v>
-      </c>
-      <c r="E11" s="5" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A12" s="5" t="s">
-        <v>130</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>137</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>138</v>
-      </c>
-      <c r="D12" s="5" t="s">
-        <v>139</v>
-      </c>
-      <c r="E12" s="5" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A13" s="5" t="s">
-        <v>130</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>140</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>141</v>
-      </c>
-      <c r="D13" s="5" t="s">
-        <v>142</v>
-      </c>
-      <c r="E13" s="5" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A14" s="5" t="s">
-        <v>130</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>143</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>144</v>
-      </c>
-      <c r="D14" s="5" t="s">
-        <v>145</v>
-      </c>
-      <c r="E14" s="5" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A15" s="5" t="s">
-        <v>130</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>146</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="D15" s="5" t="s">
-        <v>148</v>
-      </c>
-      <c r="E15" s="5" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A16" s="5" t="s">
-        <v>130</v>
-      </c>
-      <c r="B16" s="5" t="s">
-        <v>149</v>
-      </c>
-      <c r="C16" s="5" t="s">
-        <v>150</v>
-      </c>
-      <c r="D16" s="5" t="s">
-        <v>151</v>
-      </c>
-      <c r="E16" s="5" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A17" s="5" t="s">
-        <v>130</v>
-      </c>
-      <c r="B17" s="5" t="s">
-        <v>152</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>153</v>
-      </c>
-      <c r="D17" s="5" t="s">
-        <v>154</v>
-      </c>
-      <c r="E17" s="5" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A18" s="5" t="s">
-        <v>130</v>
-      </c>
-      <c r="B18" s="5" t="s">
-        <v>155</v>
-      </c>
-      <c r="C18" s="5" t="s">
-        <v>156</v>
-      </c>
-      <c r="D18" s="5" t="s">
-        <v>157</v>
-      </c>
-      <c r="E18" s="5" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A19" s="5" t="s">
-        <v>130</v>
-      </c>
-      <c r="B19" s="5" t="s">
-        <v>158</v>
-      </c>
-      <c r="C19" s="5" t="s">
-        <v>159</v>
-      </c>
-      <c r="D19" s="5" t="s">
-        <v>160</v>
-      </c>
-      <c r="E19" s="5" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A20" s="6">
-        <v>46243</v>
-      </c>
-      <c r="B20" s="5" t="s">
-        <v>161</v>
-      </c>
-      <c r="C20" s="5" t="s">
-        <v>162</v>
-      </c>
-      <c r="D20" s="5" t="s">
-        <v>163</v>
-      </c>
-      <c r="E20" s="5" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A21" s="6">
-        <v>46243</v>
-      </c>
-      <c r="B21" s="5" t="s">
-        <v>164</v>
-      </c>
-      <c r="C21" s="5" t="s">
-        <v>165</v>
-      </c>
-      <c r="D21" s="5" t="s">
-        <v>166</v>
-      </c>
-      <c r="E21" s="5" t="s">
-        <v>21</v>
+      <c r="B23" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="E23" s="4" t="s">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:E4"/>
+  <autoFilter ref="A4:E4" xr:uid="{00000000-0009-0000-0000-000003000000}"/>
   <mergeCells count="1">
     <mergeCell ref="A2:E2"/>
   </mergeCells>
@@ -2103,7 +2128,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -2114,50 +2139,54 @@
   <sheetData>
     <row r="1" spans="1:3" ht="21" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
-        <v>167</v>
+        <v>143</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
+      <c r="A2" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="B2" s="8"/>
+      <c r="C2" s="8"/>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>169</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" s="5">
+      <c r="A4" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A5" s="4">
         <v>0</v>
       </c>
-      <c r="B5" s="5"/>
-      <c r="C5" s="5"/>
+      <c r="B5" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>181</v>
+      </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" s="5" t="s">
-        <v>171</v>
-      </c>
-      <c r="B6" s="5"/>
-      <c r="C6" s="5"/>
+      <c r="A6" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="B6" s="4"/>
+      <c r="C6" s="4"/>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" s="5" t="s">
-        <v>172</v>
-      </c>
-      <c r="B7" s="5"/>
-      <c r="C7" s="5"/>
+      <c r="A7" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="B7" s="4"/>
+      <c r="C7" s="4"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:C4"/>
+  <autoFilter ref="A4:C4" xr:uid="{00000000-0009-0000-0000-000004000000}"/>
   <mergeCells count="1">
     <mergeCell ref="A2:C2"/>
   </mergeCells>
